--- a/artfynd/A 53471-2024 artfynd.xlsx
+++ b/artfynd/A 53471-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121437840</v>
+        <v>121437839</v>
       </c>
       <c r="B2" t="n">
-        <v>105186</v>
+        <v>97041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -758,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121437839</v>
+        <v>121437840</v>
       </c>
       <c r="B3" t="n">
-        <v>97041</v>
+        <v>105186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +807,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 53471-2024 artfynd.xlsx
+++ b/artfynd/A 53471-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121437839</v>
+        <v>121437840</v>
       </c>
       <c r="B2" t="n">
-        <v>97041</v>
+        <v>105199</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,25 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121437840</v>
+        <v>121437839</v>
       </c>
       <c r="B3" t="n">
-        <v>105186</v>
+        <v>97054</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,29 +811,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 53471-2024 artfynd.xlsx
+++ b/artfynd/A 53471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121437840</v>
       </c>
       <c r="B2" t="n">
-        <v>105199</v>
+        <v>105200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>121437839</v>
       </c>
       <c r="B3" t="n">
-        <v>97054</v>
+        <v>97055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53471-2024 artfynd.xlsx
+++ b/artfynd/A 53471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121437840</v>
       </c>
       <c r="B2" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>121437839</v>
       </c>
       <c r="B3" t="n">
-        <v>97055</v>
+        <v>97058</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53471-2024 artfynd.xlsx
+++ b/artfynd/A 53471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121437840</v>
       </c>
       <c r="B2" t="n">
-        <v>105203</v>
+        <v>105209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>121437839</v>
       </c>
       <c r="B3" t="n">
-        <v>97058</v>
+        <v>97064</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53471-2024 artfynd.xlsx
+++ b/artfynd/A 53471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121437840</v>
       </c>
       <c r="B2" t="n">
-        <v>105209</v>
+        <v>105210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>121437839</v>
       </c>
       <c r="B3" t="n">
-        <v>97064</v>
+        <v>97065</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53471-2024 artfynd.xlsx
+++ b/artfynd/A 53471-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121437840</v>
+        <v>121437839</v>
       </c>
       <c r="B2" t="n">
-        <v>105210</v>
+        <v>97065</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -758,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121437839</v>
+        <v>121437840</v>
       </c>
       <c r="B3" t="n">
-        <v>97065</v>
+        <v>105210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +807,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 53471-2024 artfynd.xlsx
+++ b/artfynd/A 53471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121437839</v>
       </c>
       <c r="B2" t="n">
-        <v>97065</v>
+        <v>97073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>121437840</v>
       </c>
       <c r="B3" t="n">
-        <v>105210</v>
+        <v>105218</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53471-2024 artfynd.xlsx
+++ b/artfynd/A 53471-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121437839</v>
+        <v>121437840</v>
       </c>
       <c r="B2" t="n">
-        <v>97073</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,25 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -754,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121437840</v>
+        <v>121437839</v>
       </c>
       <c r="B3" t="n">
-        <v>105218</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,29 +801,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -874,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 53471-2024 artfynd.xlsx
+++ b/artfynd/A 53471-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121437840</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,8 +908,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121437839</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>